--- a/erp-server/erp-server-wms/src/main/resources/excel/packing.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/packing.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,17 +29,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FF0D0015"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>发货单号</t>
-    </r>
+    <t>发货单号</t>
   </si>
   <si>
     <r>

--- a/erp-server/erp-server-wms/src/main/resources/excel/packing.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/packing.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>发货单号</t>
   </si>
@@ -71,30 +71,16 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>每箱实重（KG）</t>
-    </r>
+    <t>每箱实重(KG)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>每箱体积长*宽*高（CM)</t>
-    </r>
+    <t>每箱体积长(CM)</t>
+  </si>
+  <si>
+    <t>每箱体积宽(CM)</t>
+  </si>
+  <si>
+    <t>每箱体积高(CM)</t>
   </si>
 </sst>
 </file>
@@ -1076,8 +1062,8 @@
     <col min="3" max="3" width="15.125" customWidth="1"/>
     <col min="4" max="4" width="16.875" customWidth="1"/>
     <col min="5" max="5" width="27.5" customWidth="1"/>
-    <col min="6" max="6" width="12.125" customWidth="1"/>
-    <col min="7" max="7" width="10.625" customWidth="1"/>
+    <col min="6" max="6" width="22.625" customWidth="1"/>
+    <col min="7" max="7" width="22.5" customWidth="1"/>
     <col min="8" max="8" width="29" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1100,13 +1086,14 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="F1:H1"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/erp-server/erp-server-wms/src/main/resources/excel/packing.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/packing.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
-    <t>发货单号</t>
+    <t>来源单号</t>
   </si>
   <si>
     <r>

--- a/erp-server/erp-server-wms/src/main/resources/excel/packing.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/packing.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>来源单号</t>
   </si>
@@ -43,6 +43,9 @@
       </rPr>
       <t>SKU</t>
     </r>
+  </si>
+  <si>
+    <t>fnSku</t>
   </si>
   <si>
     <r>
@@ -1054,27 +1057,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="19.875" customWidth="1"/>
-    <col min="2" max="2" width="15.375" customWidth="1"/>
-    <col min="3" max="3" width="15.125" customWidth="1"/>
-    <col min="4" max="4" width="16.875" customWidth="1"/>
-    <col min="5" max="5" width="27.5" customWidth="1"/>
-    <col min="6" max="6" width="22.625" customWidth="1"/>
-    <col min="7" max="7" width="22.5" customWidth="1"/>
-    <col min="8" max="8" width="29" customWidth="1"/>
+    <col min="2" max="3" width="15.375" customWidth="1"/>
+    <col min="4" max="4" width="15.125" customWidth="1"/>
+    <col min="5" max="5" width="16.875" customWidth="1"/>
+    <col min="6" max="6" width="27.5" customWidth="1"/>
+    <col min="7" max="7" width="22.625" customWidth="1"/>
+    <col min="8" max="8" width="22.5" customWidth="1"/>
+    <col min="9" max="9" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.25" customHeight="1" spans="1:8">
+    <row r="1" ht="20.25" customHeight="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -1092,6 +1095,9 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-wms/src/main/resources/excel/packing.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/packing.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>来源单号</t>
   </si>
@@ -84,6 +84,9 @@
   </si>
   <si>
     <t>每箱体积高(CM)</t>
+  </si>
+  <si>
+    <t>客户PO号</t>
   </si>
 </sst>
 </file>
@@ -1057,7 +1060,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="19.875" customWidth="1"/>
@@ -1068,9 +1071,10 @@
     <col min="7" max="7" width="22.625" customWidth="1"/>
     <col min="8" max="8" width="22.5" customWidth="1"/>
     <col min="9" max="9" width="29" customWidth="1"/>
+    <col min="10" max="10" width="15.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.25" customHeight="1" spans="1:9">
+    <row r="1" ht="20.25" customHeight="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1098,6 +1102,9 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
